--- a/05_交付物/通俗细分版_2026-08-07/02_文档表格演示文稿与办公自动化/02-08_Office 综合处理与流程自动化/02-08_Office 综合处理与流程自动化_GitHub技能调研.xlsx
+++ b/05_交付物/通俗细分版_2026-08-07/02_文档表格演示文稿与办公自动化/02-08_Office 综合处理与流程自动化/02-08_Office 综合处理与流程自动化_GitHub技能调研.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="rId4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI技能清单" sheetId="2" r:id="rId5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类统计" sheetId="3" r:id="rId6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源清单" sheetId="4" r:id="rId7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="R11e3bd46b32f44bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI技能清单" sheetId="2" r:id="R7d23088b614648f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类统计" sheetId="3" r:id="Recb4c8fec6c04d45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源清单" sheetId="4" r:id="R6ad0f61626e74be1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1012,11 +1012,11 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:hyperlinks>
-    <x:hyperlink ref="U5" r:id="rId1"/>
-    <x:hyperlink ref="V5" r:id="rId2"/>
+    <x:hyperlink ref="U5" r:id="rIdHyperlink1"/>
+    <x:hyperlink ref="V5" r:id="rIdHyperlink2"/>
   </x:hyperlinks>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96839f4cd6ef4768"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1264,10 +1264,10 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:hyperlinks>
-    <x:hyperlink ref="B5" r:id="rId1"/>
+    <x:hyperlink ref="B5" r:id="rIdHyperlink1"/>
   </x:hyperlinks>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re428b76ea6a24262"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/05_交付物/通俗细分版_2026-08-07/02_文档表格演示文稿与办公自动化/02-08_Office 综合处理与流程自动化/02-08_Office 综合处理与流程自动化_GitHub技能调研.xlsx
+++ b/05_交付物/通俗细分版_2026-08-07/02_文档表格演示文稿与办公自动化/02-08_Office 综合处理与流程自动化/02-08_Office 综合处理与流程自动化_GitHub技能调研.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="R11e3bd46b32f44bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI技能清单" sheetId="2" r:id="R7d23088b614648f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类统计" sheetId="3" r:id="Recb4c8fec6c04d45"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源清单" sheetId="4" r:id="R6ad0f61626e74be1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="R30800f10d0904d03"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI技能清单" sheetId="2" r:id="Rfebc1b214c2e4b5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类统计" sheetId="3" r:id="Rb5c0dc5473aa43d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源清单" sheetId="4" r:id="R57a42027fae14d88"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1016,7 +1016,7 @@
     <x:hyperlink ref="V5" r:id="rIdHyperlink2"/>
   </x:hyperlinks>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96839f4cd6ef4768"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8edb70f5212245bd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1267,7 +1267,7 @@
     <x:hyperlink ref="B5" r:id="rIdHyperlink1"/>
   </x:hyperlinks>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re428b76ea6a24262"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf31c324485a9407d"/>
   </x:tableParts>
 </x:worksheet>
 </file>